--- a/update/emp_mgmt/test_data/Swarajya-Update-Employee-test-cases.xlsx
+++ b/update/emp_mgmt/test_data/Swarajya-Update-Employee-test-cases.xlsx
@@ -1497,9 +1497,9 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1549,9 +1549,9 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1601,9 +1601,9 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1704,9 +1704,9 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1807,9 +1807,9 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1959,9 +1959,9 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2010,9 +2010,9 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2061,9 +2061,9 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>

--- a/update/emp_mgmt/test_data/Swarajya-Update-Employee-test-cases.xlsx
+++ b/update/emp_mgmt/test_data/Swarajya-Update-Employee-test-cases.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Update_Positive_Flows" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Update_Negative_Flows" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update_Positive_Flows" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update_Negative_Flows" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -577,7 +577,11 @@
           <t>The employee profile is updated successfully with the new mandatory details and a confirmation message is displayed.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>AUT_TC_POS_UPD_001</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Automated</t>
@@ -1435,7 +1439,11 @@
           <t>Update submission fails and a validation error is displayed indicating the mandatory field cannot be blank.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>AUT_TC_NEG_UPD_001</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Automated</t>

--- a/update/emp_mgmt/test_data/Swarajya-Update-Employee-test-cases.xlsx
+++ b/update/emp_mgmt/test_data/Swarajya-Update-Employee-test-cases.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update_Positive_Flows" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update_Negative_Flows" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Update_Positive_Flows" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Update_Negative_Flows" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1494,7 +1494,11 @@
           <t>Update submission fails and a validation error indicating the mobile number must be exactly 10 numeric digits is displayed.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>AUT_TC_NEG_UPD_002</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Automated</t>

--- a/update/emp_mgmt/test_data/Swarajya-Update-Employee-test-cases.xlsx
+++ b/update/emp_mgmt/test_data/Swarajya-Update-Employee-test-cases.xlsx
@@ -592,9 +592,9 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,11 @@
           <t>The Gender value is updated successfully, saved, and correctly reflected when the profile is reopened.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>AUT_TC_POS_UPD_002</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Automated</t>
@@ -685,7 +689,11 @@
           <t>Every Marital Status option is selected properly, the profile is updated successfully, and a confirmation message is displayed.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>AUT_TC_POS_UPD_003</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Automated</t>
@@ -736,7 +744,11 @@
           <t>The Date of Birth is updated successfully and the profile is saved with the new date.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="n"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>AUT_TC_POS_UPD_004</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Automated</t>
@@ -787,7 +799,11 @@
           <t>The Personal Email ID is updated successfully and saved without any validation error.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>AUT_TC_POS_UPD_005</t>
+        </is>
+      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Automated</t>
@@ -840,7 +856,11 @@
           <t>Both toggle switches are updated successfully, saved, and the correct ON/OFF state is displayed after reopening the profile.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="n"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>AUT_TC_POS_UPD_006</t>
+        </is>
+      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Automated</t>
@@ -892,7 +912,11 @@
           <t>The Emergency Contact details are updated successfully and a confirmation message is displayed.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="n"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>AUT_TC_POS_UPD_007</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Automated</t>
@@ -946,7 +970,11 @@
           <t>The address details are updated successfully and saved with a confirmation message displayed.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="n"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>AUT_TC_POS_UPD_008</t>
+        </is>
+      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Automated</t>
@@ -998,7 +1026,11 @@
           <t>The employee profile is updated successfully without requiring changes to optional fields, and a confirmation message is displayed.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="n"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>AUT_TC_POS_UPD_009</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Automated</t>
@@ -1048,7 +1080,11 @@
           <t>The Employee ID field is disabled/read-only and cannot be modified by the user.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="n"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>AUT_TC_POS_UPD_010</t>
+        </is>
+      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Automated</t>
@@ -1099,7 +1135,11 @@
           <t>The Employee List reflects the newly updated details accurately for the corresponding employee.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="n"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>AUT_TC_POS_UPD_011</t>
+        </is>
+      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Automated</t>
@@ -1152,7 +1192,11 @@
           <t>The unsaved changes are discarded, and the original employee data is retained/displayed when the profile is reopened.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="n"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>AUT_TC_POS_UPD_012</t>
+        </is>
+      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Automated</t>
@@ -1203,7 +1247,11 @@
           <t>The employee profile is updated successfully with the special character retained, and a confirmation message is displayed.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="n"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>AUT_TC_POS_UPD_013</t>
+        </is>
+      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Automated</t>
@@ -1255,7 +1303,11 @@
           <t>The employee profile is updated successfully with the full-length values saved, and a confirmation message is displayed.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="n"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>AUT_TC_POS_UPD_014</t>
+        </is>
+      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Automated</t>
@@ -1310,7 +1362,11 @@
           <t>All modified fields across the different sections are saved correctly in a single update, and a confirmation message is displayed.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="n"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>AUT_TC_POS_UPD_015</t>
+        </is>
+      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Automated</t>
@@ -1550,7 +1606,11 @@
           <t>Update submission fails and a validation error indicating proper email formatting is required is displayed.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>AUT_TC_NEG_UPD_003</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Automated</t>
@@ -1602,7 +1662,11 @@
           <t>Update submission fails and validation errors indicating only alphabetic values are allowed for name fields are displayed.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="n"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>AUT_TC_NEG_UPD_004</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Automated</t>
@@ -1653,7 +1717,11 @@
           <t>Update submission fails and a validation error indicating the PIN must be a valid 6-digit numeric value is displayed.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>AUT_TC_NEG_UPD_005</t>
+        </is>
+      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Automated</t>
@@ -1664,9 +1732,9 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1773,11 @@
           <t>Update submission fails and a validation error indicating the joining date must be after the date of birth is displayed.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="n"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>AUT_TC_NEG_UPD_006</t>
+        </is>
+      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Automated</t>
@@ -1756,7 +1828,11 @@
           <t>The Employee ID field remains disabled/read-only in the UI, and any backend attempt to alter it is rejected with an appropriate error.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="n"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>AUT_TC_NEG_UPD_007</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Automated</t>
@@ -1808,7 +1884,11 @@
           <t>Update submission fails and a validation error indicating the Mobile Number/Email ID is already in use by another employee is displayed.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="n"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>AUT_TC_NEG_UPD_008</t>
+        </is>
+      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Automated</t>
@@ -1858,7 +1938,11 @@
           <t>The update is rejected, and the user is redirected to the login screen or prompted to re-authenticate (Login ID/Password/2FA) before the changes can be saved.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="n"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>AUT_TC_NEG_UPD_009</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Automated</t>
@@ -1909,7 +1993,11 @@
           <t>Update submission fails and a validation error indicating the mandatory field cannot contain only blank spaces is displayed.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="n"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>AUT_TC_NEG_UPD_010</t>
+        </is>
+      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Automated</t>
@@ -1960,7 +2048,11 @@
           <t>Update submission fails and a validation error indicating the date of birth is too recent (underage) is displayed.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="n"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>AUT_TC_NEG_UPD_011</t>
+        </is>
+      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Automated</t>
@@ -2011,7 +2103,11 @@
           <t>Update submission fails and a validation error indicating the joining date cannot be set too far in the future is displayed.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="n"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>AUT_TC_NEG_UPD_012</t>
+        </is>
+      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Automated</t>
@@ -2062,7 +2158,11 @@
           <t>Update submission fails and a validation error indicating the emergency contact number must be exactly 10 numeric digits is displayed.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="n"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>AUT_TC_NEG_UPD_013</t>
+        </is>
+      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Automated</t>
